--- a/client/public/products/pack1-pm-essentials/risk-register.xlsx
+++ b/client/public/products/pack1-pm-essentials/risk-register.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Matrix Chart" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Risk Matrix Chart'!$A$1:$H$34</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -20,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -159,8 +161,37 @@
       <color rgb="FF006100"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF0D1B2A"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF1f2937"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF9CA3AF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF0D1B2A"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -191,8 +222,23 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -215,6 +261,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB0B0B0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -226,7 +286,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -381,6 +441,40 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -827,7 +921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="B2:O34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="26" min="1" max="1"/>
@@ -845,7 +939,6 @@
     <col width="14" customWidth="1" style="26" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="30" customHeight="1" s="27">
       <c r="B2" s="28" t="inlineStr">
         <is>
@@ -860,7 +953,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="27">
       <c r="B5" s="30" t="inlineStr">
         <is>
@@ -892,7 +984,7 @@
         </is>
       </c>
       <c r="C7" s="33">
-        <f>COUNTIF(I16:I30,"HIGH")</f>
+        <f>COUNTIF(I16:I31,"HIGH")</f>
         <v/>
       </c>
       <c r="E7" s="34" t="inlineStr">
@@ -901,7 +993,7 @@
         </is>
       </c>
       <c r="F7" s="33">
-        <f>COUNTIF(D16:D30,"Technical")</f>
+        <f>COUNTIF(D16:D31,"Technical")</f>
         <v/>
       </c>
       <c r="H7" s="34" t="inlineStr">
@@ -910,7 +1002,7 @@
         </is>
       </c>
       <c r="I7" s="33">
-        <f>COUNTIF(N16:N30,"Open")</f>
+        <f>COUNTIF(N16:N31,"Open")</f>
         <v/>
       </c>
     </row>
@@ -921,7 +1013,7 @@
         </is>
       </c>
       <c r="C8" s="33">
-        <f>COUNTIF(I16:I30,"MEDIUM")</f>
+        <f>COUNTIF(I16:I31,"MEDIUM")</f>
         <v/>
       </c>
       <c r="E8" s="34" t="inlineStr">
@@ -930,7 +1022,7 @@
         </is>
       </c>
       <c r="F8" s="33">
-        <f>COUNTIF(D16:D30,"Schedule")</f>
+        <f>COUNTIF(D16:D31,"Schedule")</f>
         <v/>
       </c>
       <c r="H8" s="34" t="inlineStr">
@@ -939,7 +1031,7 @@
         </is>
       </c>
       <c r="I8" s="33">
-        <f>COUNTIF(N16:N30,"Mitigated")</f>
+        <f>COUNTIF(N16:N31,"Mitigated")</f>
         <v/>
       </c>
     </row>
@@ -950,7 +1042,7 @@
         </is>
       </c>
       <c r="C9" s="33">
-        <f>COUNTIF(I16:I30,"LOW")</f>
+        <f>COUNTIF(I16:I31,"LOW")</f>
         <v/>
       </c>
       <c r="E9" s="34" t="inlineStr">
@@ -959,7 +1051,7 @@
         </is>
       </c>
       <c r="F9" s="33">
-        <f>COUNTIF(D16:D30,"Cost")</f>
+        <f>COUNTIF(D16:D31,"Cost")</f>
         <v/>
       </c>
       <c r="H9" s="34" t="inlineStr">
@@ -968,7 +1060,7 @@
         </is>
       </c>
       <c r="I9" s="33">
-        <f>COUNTIF(N16:N30,"Closed")</f>
+        <f>COUNTIF(N16:N31,"Closed")</f>
         <v/>
       </c>
     </row>
@@ -979,7 +1071,7 @@
         </is>
       </c>
       <c r="F10" s="33">
-        <f>COUNTIF(D16:D30,"External")</f>
+        <f>COUNTIF(D16:D31,"External")</f>
         <v/>
       </c>
       <c r="H10" s="34" t="inlineStr">
@@ -988,7 +1080,7 @@
         </is>
       </c>
       <c r="I10" s="33">
-        <f>COUNTIF(N16:N30,"Accepted")</f>
+        <f>COUNTIF(N16:N31,"Accepted")</f>
         <v/>
       </c>
     </row>
@@ -999,39 +1091,35 @@
         </is>
       </c>
       <c r="F11" s="33">
-        <f>COUNTIF(D16:D30,"Programmatic")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
+        <f>COUNTIF(D16:D31,"Programmatic")</f>
+        <v/>
+      </c>
+    </row>
     <row r="16" ht="49.5" customHeight="1" s="27">
-      <c r="B16" s="37" t="inlineStr">
+      <c r="B16" s="52" t="inlineStr">
         <is>
           <t>R-001</t>
         </is>
       </c>
-      <c r="C16" s="38" t="inlineStr">
+      <c r="C16" s="53" t="inlineStr">
         <is>
           <t>Software Integration Failure</t>
         </is>
       </c>
-      <c r="D16" s="37" t="inlineStr">
+      <c r="D16" s="52" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="E16" s="39" t="inlineStr">
+      <c r="E16" s="54" t="inlineStr">
         <is>
           <t>Integration of legacy C4ISR systems with new cloud-based architecture may fail due to incompatible interfaces and undocumented APIs</t>
         </is>
       </c>
-      <c r="F16" s="37" t="n">
+      <c r="F16" s="52" t="n">
         <v>4</v>
       </c>
-      <c r="G16" s="37" t="n">
+      <c r="G16" s="52" t="n">
         <v>5</v>
       </c>
       <c r="H16" s="40">
@@ -1042,58 +1130,58 @@
         <f>IF(H16&gt;=15,"HIGH",IF(H16&gt;=8,"MEDIUM","LOW"))</f>
         <v/>
       </c>
-      <c r="J16" s="39" t="inlineStr">
+      <c r="J16" s="54" t="inlineStr">
         <is>
           <t>Conduct early integration testing in sprint 2; establish interface control documents (ICDs) before CDR</t>
         </is>
       </c>
-      <c r="K16" s="39" t="inlineStr">
+      <c r="K16" s="54" t="inlineStr">
         <is>
           <t>Revert to point-to-point integration with middleware adapter layer</t>
         </is>
       </c>
-      <c r="L16" s="37" t="inlineStr">
+      <c r="L16" s="52" t="inlineStr">
         <is>
           <t>Systems Engineer</t>
         </is>
       </c>
-      <c r="M16" s="41" t="n">
+      <c r="M16" s="55" t="n">
         <v>46134</v>
       </c>
-      <c r="N16" s="37" t="inlineStr">
+      <c r="N16" s="52" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="O16" s="41" t="n">
+      <c r="O16" s="55" t="n">
         <v>46104</v>
       </c>
     </row>
     <row r="17" ht="49.5" customHeight="1" s="27">
-      <c r="B17" s="37" t="inlineStr">
+      <c r="B17" s="52" t="inlineStr">
         <is>
           <t>R-002</t>
         </is>
       </c>
-      <c r="C17" s="38" t="inlineStr">
+      <c r="C17" s="53" t="inlineStr">
         <is>
           <t>Key Personnel Departure</t>
         </is>
       </c>
-      <c r="D17" s="37" t="inlineStr">
+      <c r="D17" s="52" t="inlineStr">
         <is>
           <t>Programmatic</t>
         </is>
       </c>
-      <c r="E17" s="39" t="inlineStr">
+      <c r="E17" s="54" t="inlineStr">
         <is>
           <t>Program Manager or Technical Lead may depart during performance period, causing knowledge loss and schedule delays</t>
         </is>
       </c>
-      <c r="F17" s="37" t="n">
+      <c r="F17" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="G17" s="37" t="n">
+      <c r="G17" s="52" t="n">
         <v>4</v>
       </c>
       <c r="H17" s="40">
@@ -1104,58 +1192,58 @@
         <f>IF(H17&gt;=15,"HIGH",IF(H17&gt;=8,"MEDIUM","LOW"))</f>
         <v/>
       </c>
-      <c r="J17" s="39" t="inlineStr">
+      <c r="J17" s="54" t="inlineStr">
         <is>
           <t>Cross-train deputy PM; maintain knowledge repository; include retention incentives in compensation plan</t>
         </is>
       </c>
-      <c r="K17" s="39" t="inlineStr">
+      <c r="K17" s="54" t="inlineStr">
         <is>
           <t>Activate pre-identified replacement from bench; execute 30-day transition plan</t>
         </is>
       </c>
-      <c r="L17" s="37" t="inlineStr">
+      <c r="L17" s="52" t="inlineStr">
         <is>
           <t>HR Director</t>
         </is>
       </c>
-      <c r="M17" s="41" t="n">
+      <c r="M17" s="55" t="n">
         <v>46164</v>
       </c>
-      <c r="N17" s="37" t="inlineStr">
+      <c r="N17" s="52" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="O17" s="41" t="n">
+      <c r="O17" s="55" t="n">
         <v>46104</v>
       </c>
     </row>
     <row r="18" ht="49.5" customHeight="1" s="27">
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="52" t="inlineStr">
         <is>
           <t>R-003</t>
         </is>
       </c>
-      <c r="C18" s="38" t="inlineStr">
+      <c r="C18" s="53" t="inlineStr">
         <is>
           <t>Requirements Creep</t>
         </is>
       </c>
-      <c r="D18" s="37" t="inlineStr">
+      <c r="D18" s="52" t="inlineStr">
         <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="E18" s="39" t="inlineStr">
+      <c r="E18" s="54" t="inlineStr">
         <is>
           <t>Government may issue numerous contract modifications expanding scope without proportional schedule/cost adjustments</t>
         </is>
       </c>
-      <c r="F18" s="37" t="n">
+      <c r="F18" s="52" t="n">
         <v>4</v>
       </c>
-      <c r="G18" s="37" t="n">
+      <c r="G18" s="52" t="n">
         <v>4</v>
       </c>
       <c r="H18" s="40">
@@ -1166,58 +1254,58 @@
         <f>IF(H18&gt;=15,"HIGH",IF(H18&gt;=8,"MEDIUM","LOW"))</f>
         <v/>
       </c>
-      <c r="J18" s="39" t="inlineStr">
+      <c r="J18" s="54" t="inlineStr">
         <is>
           <t>Establish formal change control board; track all requirements changes against baseline; negotiate equitable adjustments promptly</t>
         </is>
       </c>
-      <c r="K18" s="39" t="inlineStr">
+      <c r="K18" s="54" t="inlineStr">
         <is>
           <t>Invoke REA process; request stop-work on unfunded requirements until modification is executed</t>
         </is>
       </c>
-      <c r="L18" s="37" t="inlineStr">
+      <c r="L18" s="52" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="M18" s="41" t="n">
+      <c r="M18" s="55" t="n">
         <v>46149</v>
       </c>
-      <c r="N18" s="37" t="inlineStr">
+      <c r="N18" s="52" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="O18" s="41" t="n">
+      <c r="O18" s="55" t="n">
         <v>46104</v>
       </c>
     </row>
     <row r="19" ht="49.5" customHeight="1" s="27">
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="52" t="inlineStr">
         <is>
           <t>R-004</t>
         </is>
       </c>
-      <c r="C19" s="38" t="inlineStr">
+      <c r="C19" s="53" t="inlineStr">
         <is>
           <t>Funding Shortfall / CR Impact</t>
         </is>
       </c>
-      <c r="D19" s="37" t="inlineStr">
+      <c r="D19" s="52" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="E19" s="39" t="inlineStr">
+      <c r="E19" s="54" t="inlineStr">
         <is>
           <t>Continuing Resolution or sequestration may reduce available program funding below planned obligation levels</t>
         </is>
       </c>
-      <c r="F19" s="37" t="n">
+      <c r="F19" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="G19" s="37" t="n">
+      <c r="G19" s="52" t="n">
         <v>5</v>
       </c>
       <c r="H19" s="40">
@@ -1228,58 +1316,58 @@
         <f>IF(H19&gt;=15,"HIGH",IF(H19&gt;=8,"MEDIUM","LOW"))</f>
         <v/>
       </c>
-      <c r="J19" s="39" t="inlineStr">
+      <c r="J19" s="54" t="inlineStr">
         <is>
           <t>Maintain prioritized requirements backlog; identify minimum viable capability set; coordinate with PEO on funding alternatives</t>
         </is>
       </c>
-      <c r="K19" s="39" t="inlineStr">
+      <c r="K19" s="54" t="inlineStr">
         <is>
           <t>Descope optional CLINs; defer non-critical deliverables to subsequent option years</t>
         </is>
       </c>
-      <c r="L19" s="37" t="inlineStr">
+      <c r="L19" s="52" t="inlineStr">
         <is>
           <t>Finance Director</t>
         </is>
       </c>
-      <c r="M19" s="41" t="n">
+      <c r="M19" s="55" t="n">
         <v>46194</v>
       </c>
-      <c r="N19" s="37" t="inlineStr">
+      <c r="N19" s="52" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="O19" s="41" t="n">
+      <c r="O19" s="55" t="n">
         <v>46104</v>
       </c>
     </row>
     <row r="20" ht="49.5" customHeight="1" s="27">
-      <c r="B20" s="37" t="inlineStr">
+      <c r="B20" s="52" t="inlineStr">
         <is>
           <t>R-005</t>
         </is>
       </c>
-      <c r="C20" s="38" t="inlineStr">
+      <c r="C20" s="53" t="inlineStr">
         <is>
           <t>Subcontractor Performance</t>
         </is>
       </c>
-      <c r="D20" s="37" t="inlineStr">
+      <c r="D20" s="52" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="E20" s="39" t="inlineStr">
+      <c r="E20" s="54" t="inlineStr">
         <is>
           <t>Critical subcontractor (cybersecurity toolset provider) may fail to deliver on schedule or meet quality standards</t>
         </is>
       </c>
-      <c r="F20" s="37" t="n">
+      <c r="F20" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="G20" s="37" t="n">
+      <c r="G20" s="52" t="n">
         <v>4</v>
       </c>
       <c r="H20" s="40">
@@ -1290,58 +1378,58 @@
         <f>IF(H20&gt;=15,"HIGH",IF(H20&gt;=8,"MEDIUM","LOW"))</f>
         <v/>
       </c>
-      <c r="J20" s="39" t="inlineStr">
+      <c r="J20" s="54" t="inlineStr">
         <is>
           <t>Conduct monthly sub performance reviews; include liquidated damages clause; maintain qualified alternate vendor list</t>
         </is>
       </c>
-      <c r="K20" s="39" t="inlineStr">
+      <c r="K20" s="54" t="inlineStr">
         <is>
           <t>Activate alternate vendor under pre-negotiated teaming agreement; absorb initial ramp-up costs</t>
         </is>
       </c>
-      <c r="L20" s="37" t="inlineStr">
+      <c r="L20" s="52" t="inlineStr">
         <is>
           <t>Subcontracts Mgr</t>
         </is>
       </c>
-      <c r="M20" s="41" t="n">
+      <c r="M20" s="55" t="n">
         <v>46134</v>
       </c>
-      <c r="N20" s="37" t="inlineStr">
+      <c r="N20" s="52" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="O20" s="41" t="n">
+      <c r="O20" s="55" t="n">
         <v>46104</v>
       </c>
     </row>
     <row r="21" ht="49.5" customHeight="1" s="27">
-      <c r="B21" s="37" t="inlineStr">
+      <c r="B21" s="52" t="inlineStr">
         <is>
           <t>R-006</t>
         </is>
       </c>
-      <c r="C21" s="38" t="inlineStr">
+      <c r="C21" s="53" t="inlineStr">
         <is>
           <t>CMMC Certification Delay</t>
         </is>
       </c>
-      <c r="D21" s="37" t="inlineStr">
+      <c r="D21" s="52" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="E21" s="39" t="inlineStr">
+      <c r="E21" s="54" t="inlineStr">
         <is>
           <t>CMMC Phase 1 (self-assessment, Level 2) is active as of Nov 10, 2025. Phase 2 requires a C3PAO third-party assessment, mandatory by Nov 10, 2026. Organization must complete C3PAO assessment before Phase 2 deadline to remain eligible for DoD contracts involving CUI.</t>
         </is>
       </c>
-      <c r="F21" s="37" t="n">
+      <c r="F21" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="G21" s="37" t="n">
+      <c r="G21" s="52" t="n">
         <v>5</v>
       </c>
       <c r="H21" s="40">
@@ -1352,58 +1440,58 @@
         <f>IF(H21&gt;=15,"HIGH",IF(H21&gt;=8,"MEDIUM","LOW"))</f>
         <v/>
       </c>
-      <c r="J21" s="39" t="inlineStr">
+      <c r="J21" s="54" t="inlineStr">
         <is>
           <t>Complete CMMC Level 2 self-assessment (Phase 1) immediately; remediate any POA&amp;M gaps. Engage accredited C3PAO assessor NLT Q1 2026 to schedule Phase 2 assessment before the Nov 10, 2026 mandatory deadline. Track via CMMC AB Marketplace.</t>
         </is>
       </c>
-      <c r="K21" s="39" t="inlineStr">
+      <c r="K21" s="54" t="inlineStr">
         <is>
           <t>If C3PAO assessment cannot be completed before Nov 10, 2026, consult CO on contract impact and explore interim authorization options; ensure SPRS score reflects current NIST 800-171 implementation posture.</t>
         </is>
       </c>
-      <c r="L21" s="37" t="inlineStr">
+      <c r="L21" s="52" t="inlineStr">
         <is>
           <t>ISSM</t>
         </is>
       </c>
-      <c r="M21" s="41" t="n">
+      <c r="M21" s="55" t="n">
         <v>46224</v>
       </c>
-      <c r="N21" s="37" t="inlineStr">
+      <c r="N21" s="52" t="inlineStr">
         <is>
           <t>Mitigated</t>
         </is>
       </c>
-      <c r="O21" s="41" t="n">
+      <c r="O21" s="55" t="n">
         <v>46104</v>
       </c>
     </row>
     <row r="22" ht="49.5" customHeight="1" s="27">
-      <c r="B22" s="37" t="inlineStr">
+      <c r="B22" s="52" t="inlineStr">
         <is>
           <t>R-007</t>
         </is>
       </c>
-      <c r="C22" s="38" t="inlineStr">
+      <c r="C22" s="53" t="inlineStr">
         <is>
           <t>Test Environment Unavailability</t>
         </is>
       </c>
-      <c r="D22" s="37" t="inlineStr">
+      <c r="D22" s="52" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="E22" s="39" t="inlineStr">
+      <c r="E22" s="54" t="inlineStr">
         <is>
           <t>Government-furnished test range or lab environment may not be available during scheduled test windows</t>
         </is>
       </c>
-      <c r="F22" s="37" t="n">
+      <c r="F22" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="G22" s="37" t="n">
+      <c r="G22" s="52" t="n">
         <v>3</v>
       </c>
       <c r="H22" s="40">
@@ -1414,58 +1502,58 @@
         <f>IF(H22&gt;=15,"HIGH",IF(H22&gt;=8,"MEDIUM","LOW"))</f>
         <v/>
       </c>
-      <c r="J22" s="39" t="inlineStr">
+      <c r="J22" s="54" t="inlineStr">
         <is>
           <t>Reserve test windows 90 days in advance; develop simulation environment for initial testing; coordinate with range scheduling office</t>
         </is>
       </c>
-      <c r="K22" s="39" t="inlineStr">
+      <c r="K22" s="54" t="inlineStr">
         <is>
           <t>Use contractor lab environment with government-approved test procedures; reschedule to next available window</t>
         </is>
       </c>
-      <c r="L22" s="37" t="inlineStr">
+      <c r="L22" s="52" t="inlineStr">
         <is>
           <t>Test Director</t>
         </is>
       </c>
-      <c r="M22" s="41" t="n">
+      <c r="M22" s="55" t="n">
         <v>46149</v>
       </c>
-      <c r="N22" s="37" t="inlineStr">
+      <c r="N22" s="52" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="O22" s="41" t="n">
+      <c r="O22" s="55" t="n">
         <v>46104</v>
       </c>
     </row>
     <row r="23" ht="49.5" customHeight="1" s="27">
-      <c r="B23" s="37" t="inlineStr">
+      <c r="B23" s="52" t="inlineStr">
         <is>
           <t>R-008</t>
         </is>
       </c>
-      <c r="C23" s="38" t="inlineStr">
+      <c r="C23" s="53" t="inlineStr">
         <is>
           <t>Data Rights Dispute</t>
         </is>
       </c>
-      <c r="D23" s="37" t="inlineStr">
+      <c r="D23" s="52" t="inlineStr">
         <is>
           <t>Programmatic</t>
         </is>
       </c>
-      <c r="E23" s="39" t="inlineStr">
+      <c r="E23" s="54" t="inlineStr">
         <is>
           <t>Disagreement with government over technical data rights (DFARS 252.227-7013) may delay deliverable acceptance</t>
         </is>
       </c>
-      <c r="F23" s="37" t="n">
+      <c r="F23" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="37" t="n">
+      <c r="G23" s="52" t="n">
         <v>4</v>
       </c>
       <c r="H23" s="40">
@@ -1476,58 +1564,58 @@
         <f>IF(H23&gt;=15,"HIGH",IF(H23&gt;=8,"MEDIUM","LOW"))</f>
         <v/>
       </c>
-      <c r="J23" s="39" t="inlineStr">
+      <c r="J23" s="54" t="inlineStr">
         <is>
           <t>Document all data rights assertions in proposal; maintain IP development records; engage legal counsel early</t>
         </is>
       </c>
-      <c r="K23" s="39" t="inlineStr">
+      <c r="K23" s="54" t="inlineStr">
         <is>
           <t>Negotiate limited rights license; escalate to CO for determination; consider ASBCA claim if unresolved</t>
         </is>
       </c>
-      <c r="L23" s="37" t="inlineStr">
+      <c r="L23" s="52" t="inlineStr">
         <is>
           <t>Legal Counsel</t>
         </is>
       </c>
-      <c r="M23" s="41" t="n">
+      <c r="M23" s="55" t="n">
         <v>46164</v>
       </c>
-      <c r="N23" s="37" t="inlineStr">
+      <c r="N23" s="52" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="O23" s="41" t="n">
+      <c r="O23" s="55" t="n">
         <v>46104</v>
       </c>
     </row>
     <row r="24" ht="49.5" customHeight="1" s="27">
-      <c r="B24" s="37" t="inlineStr">
+      <c r="B24" s="52" t="inlineStr">
         <is>
           <t>R-009</t>
         </is>
       </c>
-      <c r="C24" s="38" t="inlineStr">
+      <c r="C24" s="53" t="inlineStr">
         <is>
           <t>EVM Compliance Gaps</t>
         </is>
       </c>
-      <c r="D24" s="37" t="inlineStr">
+      <c r="D24" s="52" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="E24" s="39" t="inlineStr">
+      <c r="E24" s="54" t="inlineStr">
         <is>
           <t>Earned Value Management System may not meet ANSI/EIA-748 standards, resulting in DCMA surveillance findings</t>
         </is>
       </c>
-      <c r="F24" s="37" t="n">
+      <c r="F24" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="37" t="n">
+      <c r="G24" s="52" t="n">
         <v>3</v>
       </c>
       <c r="H24" s="40">
@@ -1538,58 +1626,58 @@
         <f>IF(H24&gt;=15,"HIGH",IF(H24&gt;=8,"MEDIUM","LOW"))</f>
         <v/>
       </c>
-      <c r="J24" s="39" t="inlineStr">
+      <c r="J24" s="54" t="inlineStr">
         <is>
           <t>Conduct EVMS self-assessment; train all CAMs on EVM procedures; schedule pre-IBR dry run</t>
         </is>
       </c>
-      <c r="K24" s="39" t="inlineStr">
+      <c r="K24" s="54" t="inlineStr">
         <is>
           <t>Engage EVM consultant for remediation; request corrective action timeline extension from DCMA</t>
         </is>
       </c>
-      <c r="L24" s="37" t="inlineStr">
+      <c r="L24" s="52" t="inlineStr">
         <is>
           <t>Finance Director</t>
         </is>
       </c>
-      <c r="M24" s="41" t="n">
+      <c r="M24" s="55" t="n">
         <v>46134</v>
       </c>
-      <c r="N24" s="37" t="inlineStr">
+      <c r="N24" s="52" t="inlineStr">
         <is>
           <t>Mitigated</t>
         </is>
       </c>
-      <c r="O24" s="41" t="n">
+      <c r="O24" s="55" t="n">
         <v>46104</v>
       </c>
     </row>
     <row r="25" ht="49.5" customHeight="1" s="27">
-      <c r="B25" s="37" t="inlineStr">
+      <c r="B25" s="52" t="inlineStr">
         <is>
           <t>R-010</t>
         </is>
       </c>
-      <c r="C25" s="38" t="inlineStr">
+      <c r="C25" s="53" t="inlineStr">
         <is>
           <t>Supply Chain Disruption</t>
         </is>
       </c>
-      <c r="D25" s="37" t="inlineStr">
+      <c r="D25" s="52" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="E25" s="39" t="inlineStr">
+      <c r="E25" s="54" t="inlineStr">
         <is>
           <t>Critical hardware components (FPGA chips, ruggedized servers) may face extended lead times exceeding 6 months</t>
         </is>
       </c>
-      <c r="F25" s="37" t="n">
+      <c r="F25" s="52" t="n">
         <v>4</v>
       </c>
-      <c r="G25" s="37" t="n">
+      <c r="G25" s="52" t="n">
         <v>3</v>
       </c>
       <c r="H25" s="40">
@@ -1600,58 +1688,58 @@
         <f>IF(H25&gt;=15,"HIGH",IF(H25&gt;=8,"MEDIUM","LOW"))</f>
         <v/>
       </c>
-      <c r="J25" s="39" t="inlineStr">
+      <c r="J25" s="54" t="inlineStr">
         <is>
           <t>Order long-lead items at contract award; qualify multiple vendors; maintain safety stock for critical components</t>
         </is>
       </c>
-      <c r="K25" s="39" t="inlineStr">
+      <c r="K25" s="54" t="inlineStr">
         <is>
           <t>Redesign with available commercial alternatives; negotiate schedule relief through REA</t>
         </is>
       </c>
-      <c r="L25" s="37" t="inlineStr">
+      <c r="L25" s="52" t="inlineStr">
         <is>
           <t>Logistics Mgr</t>
         </is>
       </c>
-      <c r="M25" s="41" t="n">
+      <c r="M25" s="55" t="n">
         <v>46119</v>
       </c>
-      <c r="N25" s="37" t="inlineStr">
+      <c r="N25" s="52" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="O25" s="41" t="n">
+      <c r="O25" s="55" t="n">
         <v>46104</v>
       </c>
     </row>
     <row r="26" ht="49.5" customHeight="1" s="27">
-      <c r="B26" s="37" t="inlineStr">
+      <c r="B26" s="52" t="inlineStr">
         <is>
           <t>R-011</t>
         </is>
       </c>
-      <c r="C26" s="38" t="inlineStr">
+      <c r="C26" s="53" t="inlineStr">
         <is>
           <t>Clearance Processing Delays</t>
         </is>
       </c>
-      <c r="D26" s="37" t="inlineStr">
+      <c r="D26" s="52" t="inlineStr">
         <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="E26" s="39" t="inlineStr">
+      <c r="E26" s="54" t="inlineStr">
         <is>
           <t>Personnel security clearance investigations may exceed expected timelines, delaying staffing of classified positions</t>
         </is>
       </c>
-      <c r="F26" s="37" t="n">
+      <c r="F26" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="G26" s="37" t="n">
+      <c r="G26" s="52" t="n">
         <v>3</v>
       </c>
       <c r="H26" s="40">
@@ -1662,58 +1750,58 @@
         <f>IF(H26&gt;=15,"HIGH",IF(H26&gt;=8,"MEDIUM","LOW"))</f>
         <v/>
       </c>
-      <c r="J26" s="39" t="inlineStr">
+      <c r="J26" s="54" t="inlineStr">
         <is>
           <t>Submit clearance requests immediately upon contract award; utilize interim clearances where permissible; pre-identify cleared alternates</t>
         </is>
       </c>
-      <c r="K26" s="39" t="inlineStr">
+      <c r="K26" s="54" t="inlineStr">
         <is>
           <t>Assign cleared personnel from other programs temporarily; adjust task sequencing to prioritize unclassified work</t>
         </is>
       </c>
-      <c r="L26" s="37" t="inlineStr">
+      <c r="L26" s="52" t="inlineStr">
         <is>
           <t>FSO</t>
         </is>
       </c>
-      <c r="M26" s="41" t="n">
+      <c r="M26" s="55" t="n">
         <v>46134</v>
       </c>
-      <c r="N26" s="37" t="inlineStr">
+      <c r="N26" s="52" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="O26" s="41" t="n">
+      <c r="O26" s="55" t="n">
         <v>46104</v>
       </c>
     </row>
     <row r="27" ht="49.5" customHeight="1" s="27">
-      <c r="B27" s="37" t="inlineStr">
+      <c r="B27" s="52" t="inlineStr">
         <is>
           <t>R-012</t>
         </is>
       </c>
-      <c r="C27" s="38" t="inlineStr">
+      <c r="C27" s="53" t="inlineStr">
         <is>
           <t>Technical Debt Accumulation</t>
         </is>
       </c>
-      <c r="D27" s="37" t="inlineStr">
+      <c r="D27" s="52" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="E27" s="39" t="inlineStr">
+      <c r="E27" s="54" t="inlineStr">
         <is>
           <t>Aggressive delivery schedule may force shortcuts in code quality, increasing defect rates and long-term maintenance costs</t>
         </is>
       </c>
-      <c r="F27" s="37" t="n">
+      <c r="F27" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="G27" s="37" t="n">
+      <c r="G27" s="52" t="n">
         <v>3</v>
       </c>
       <c r="H27" s="40">
@@ -1724,58 +1812,58 @@
         <f>IF(H27&gt;=15,"HIGH",IF(H27&gt;=8,"MEDIUM","LOW"))</f>
         <v/>
       </c>
-      <c r="J27" s="39" t="inlineStr">
+      <c r="J27" s="54" t="inlineStr">
         <is>
           <t>Allocate 20% sprint capacity for refactoring; enforce code review gates; track technical debt backlog</t>
         </is>
       </c>
-      <c r="K27" s="39" t="inlineStr">
+      <c r="K27" s="54" t="inlineStr">
         <is>
           <t>Dedicate full sprint to debt reduction when defect rate exceeds threshold; engage additional developers</t>
         </is>
       </c>
-      <c r="L27" s="37" t="inlineStr">
+      <c r="L27" s="52" t="inlineStr">
         <is>
           <t>Tech Lead</t>
         </is>
       </c>
-      <c r="M27" s="41" t="n">
+      <c r="M27" s="55" t="n">
         <v>46164</v>
       </c>
-      <c r="N27" s="37" t="inlineStr">
+      <c r="N27" s="52" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="O27" s="41" t="n">
+      <c r="O27" s="55" t="n">
         <v>46104</v>
       </c>
     </row>
     <row r="28" ht="49.5" customHeight="1" s="27">
-      <c r="B28" s="37" t="inlineStr">
+      <c r="B28" s="52" t="inlineStr">
         <is>
           <t>R-013</t>
         </is>
       </c>
-      <c r="C28" s="38" t="inlineStr">
+      <c r="C28" s="53" t="inlineStr">
         <is>
           <t>Government Stakeholder Turnover</t>
         </is>
       </c>
-      <c r="D28" s="37" t="inlineStr">
+      <c r="D28" s="52" t="inlineStr">
         <is>
           <t>Programmatic</t>
         </is>
       </c>
-      <c r="E28" s="39" t="inlineStr">
+      <c r="E28" s="54" t="inlineStr">
         <is>
           <t>COR or program office key personnel may rotate, requiring re-education and potentially changing program priorities</t>
         </is>
       </c>
-      <c r="F28" s="37" t="n">
+      <c r="F28" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="G28" s="37" t="n">
+      <c r="G28" s="52" t="n">
         <v>2</v>
       </c>
       <c r="H28" s="40">
@@ -1786,58 +1874,58 @@
         <f>IF(H28&gt;=15,"HIGH",IF(H28&gt;=8,"MEDIUM","LOW"))</f>
         <v/>
       </c>
-      <c r="J28" s="39" t="inlineStr">
+      <c r="J28" s="54" t="inlineStr">
         <is>
           <t>Maintain comprehensive program documentation; build relationships across the program office; brief incoming personnel proactively</t>
         </is>
       </c>
-      <c r="K28" s="39" t="inlineStr">
+      <c r="K28" s="54" t="inlineStr">
         <is>
           <t>Request transition meeting with outgoing/incoming COR; provide program status briefing package</t>
         </is>
       </c>
-      <c r="L28" s="37" t="inlineStr">
+      <c r="L28" s="52" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="M28" s="41" t="n">
+      <c r="M28" s="55" t="n">
         <v>46194</v>
       </c>
-      <c r="N28" s="37" t="inlineStr">
+      <c r="N28" s="52" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="O28" s="41" t="n">
+      <c r="O28" s="55" t="n">
         <v>46104</v>
       </c>
     </row>
     <row r="29" ht="49.5" customHeight="1" s="27">
-      <c r="B29" s="37" t="inlineStr">
+      <c r="B29" s="52" t="inlineStr">
         <is>
           <t>R-014</t>
         </is>
       </c>
-      <c r="C29" s="38" t="inlineStr">
+      <c r="C29" s="53" t="inlineStr">
         <is>
           <t>Protest Delays Contract Start</t>
         </is>
       </c>
-      <c r="D29" s="37" t="inlineStr">
+      <c r="D29" s="52" t="inlineStr">
         <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="E29" s="39" t="inlineStr">
+      <c r="E29" s="54" t="inlineStr">
         <is>
           <t>Losing offeror may file GAO protest, delaying contract award by 60-100 days and compressing performance schedule</t>
         </is>
       </c>
-      <c r="F29" s="37" t="n">
+      <c r="F29" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="G29" s="37" t="n">
+      <c r="G29" s="52" t="n">
         <v>4</v>
       </c>
       <c r="H29" s="40">
@@ -1848,58 +1936,58 @@
         <f>IF(H29&gt;=15,"HIGH",IF(H29&gt;=8,"MEDIUM","LOW"))</f>
         <v/>
       </c>
-      <c r="J29" s="39" t="inlineStr">
+      <c r="J29" s="54" t="inlineStr">
         <is>
           <t>Build schedule float into early milestones; prepare mobilization plan executable on short notice; maintain team availability during protest</t>
         </is>
       </c>
-      <c r="K29" s="39" t="inlineStr">
+      <c r="K29" s="54" t="inlineStr">
         <is>
           <t>Compress initial transition period; request schedule adjustment through contract modification</t>
         </is>
       </c>
-      <c r="L29" s="37" t="inlineStr">
+      <c r="L29" s="52" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="M29" s="41" t="n">
+      <c r="M29" s="55" t="n">
         <v>46119</v>
       </c>
-      <c r="N29" s="37" t="inlineStr">
+      <c r="N29" s="52" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="O29" s="41" t="n">
+      <c r="O29" s="55" t="n">
         <v>46104</v>
       </c>
     </row>
     <row r="30" ht="49.5" customHeight="1" s="27">
-      <c r="B30" s="37" t="inlineStr">
+      <c r="B30" s="52" t="inlineStr">
         <is>
           <t>R-015</t>
         </is>
       </c>
-      <c r="C30" s="38" t="inlineStr">
+      <c r="C30" s="53" t="inlineStr">
         <is>
           <t>Nunn-McCurdy Breach Risk</t>
         </is>
       </c>
-      <c r="D30" s="37" t="inlineStr">
+      <c r="D30" s="52" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="E30" s="39" t="inlineStr">
+      <c r="E30" s="54" t="inlineStr">
         <is>
           <t>Program cost growth may approach Nunn-McCurdy unit cost thresholds, triggering Congressional notification and potential cancellation review</t>
         </is>
       </c>
-      <c r="F30" s="37" t="n">
+      <c r="F30" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="37" t="n">
+      <c r="G30" s="52" t="n">
         <v>5</v>
       </c>
       <c r="H30" s="40">
@@ -1910,43 +1998,107 @@
         <f>IF(H30&gt;=15,"HIGH",IF(H30&gt;=8,"MEDIUM","LOW"))</f>
         <v/>
       </c>
-      <c r="J30" s="39" t="inlineStr">
+      <c r="J30" s="54" t="inlineStr">
         <is>
           <t>Monitor unit cost trends monthly against APB thresholds; report cost variances exceeding 5% immediately to PEO</t>
         </is>
       </c>
-      <c r="K30" s="39" t="inlineStr">
+      <c r="K30" s="54" t="inlineStr">
         <is>
           <t>Prepare program restructure brief; identify cost reduction opportunities; coordinate with CAPE for independent cost estimate</t>
         </is>
       </c>
-      <c r="L30" s="37" t="inlineStr">
+      <c r="L30" s="52" t="inlineStr">
         <is>
           <t>Finance Director</t>
         </is>
       </c>
-      <c r="M30" s="41" t="n">
+      <c r="M30" s="55" t="n">
         <v>46194</v>
       </c>
-      <c r="N30" s="37" t="inlineStr">
+      <c r="N30" s="52" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="O30" s="41" t="n">
+      <c r="O30" s="55" t="n">
         <v>46104</v>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32"/>
+    <row r="31">
+      <c r="B31" s="52" t="inlineStr">
+        <is>
+          <t>R-016</t>
+        </is>
+      </c>
+      <c r="C31" s="53" t="inlineStr">
+        <is>
+          <t>CMMC Level 2 Non-Compliance</t>
+        </is>
+      </c>
+      <c r="D31" s="52" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="E31" s="54" t="inlineStr">
+        <is>
+          <t>Subcontractors handling Controlled Unclassified Information (CUI) may not complete required C3PAO third-party assessment before CMMC Phase 2 takes effect Nov 10, 2026, risking their eligibility to remain on contract</t>
+        </is>
+      </c>
+      <c r="F31" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="H31" s="40">
+        <f>F31*G31</f>
+        <v/>
+      </c>
+      <c r="I31" s="40">
+        <f>IF(H31&gt;=15,"HIGH",IF(H31&gt;=8,"MEDIUM","LOW"))</f>
+        <v/>
+      </c>
+      <c r="J31" s="54" t="inlineStr">
+        <is>
+          <t>Confirm CMMC Level 2 self-assessment status for every subcontractor handling CUI now; require proof of scheduled C3PAO assessment; fund the assessment cost through a subcontract modification if needed</t>
+        </is>
+      </c>
+      <c r="K31" s="54" t="inlineStr">
+        <is>
+          <t>Pre-qualify an alternate subcontractor already holding current CMMC Level 2 certification; be ready to transition CUI-handling work on short notice</t>
+        </is>
+      </c>
+      <c r="L31" s="52" t="inlineStr">
+        <is>
+          <t>Subcontracts Mgr</t>
+        </is>
+      </c>
+      <c r="M31" s="55" t="n">
+        <v>46296</v>
+      </c>
+      <c r="N31" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O31" s="55" t="n">
+        <v>46266</v>
+      </c>
+    </row>
     <row r="33" ht="15" customHeight="1" s="27">
-      <c r="B33" s="42" t="inlineStr">
+      <c r="B33" s="42" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="26" t="inlineStr">
         <is>
           <t>Template by Acqlerate — Defense Acquisitions Academy | www.acqlerate.com</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="3">
     <mergeCell ref="B33:O33"/>
     <mergeCell ref="B3:O3"/>
@@ -2003,17 +2155,20 @@
   <sheetPr filterMode="0">
     <tabColor rgb="FF01696F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="B2:G36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="26" min="1" max="1"/>
-    <col width="26" customWidth="1" style="26" min="2" max="2"/>
-    <col width="16" customWidth="1" style="26" min="3" max="7"/>
+    <col width="22" customWidth="1" style="26" min="2" max="2"/>
+    <col width="17" customWidth="1" style="26" min="3" max="7"/>
+    <col width="17" customWidth="1" style="27" min="4" max="4"/>
+    <col width="17" customWidth="1" style="27" min="5" max="5"/>
+    <col width="17" customWidth="1" style="27" min="6" max="6"/>
+    <col width="17" customWidth="1" style="27" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="30" customHeight="1" s="27">
       <c r="B2" s="43" t="inlineStr">
         <is>
@@ -2028,7 +2183,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="27">
       <c r="B5" s="44" t="inlineStr">
         <is>
@@ -2171,8 +2325,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12"/>
     <row r="13" ht="15" customHeight="1" s="27">
       <c r="B13" s="30" t="inlineStr">
         <is>
@@ -2216,8 +2368,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18"/>
     <row r="19" ht="15" customHeight="1" s="27">
       <c r="B19" s="42" t="inlineStr">
         <is>
@@ -2225,7 +2375,210 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="B22" s="56" t="inlineStr">
+        <is>
+          <t>Where Your Risks Land</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="57" t="inlineStr">
+        <is>
+          <t>Pulls live from the Risk Register. Print this page and drop it straight into your weekly program review slide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="58" t="inlineStr">
+        <is>
+          <t>Probability ↓  /  Impact →</t>
+        </is>
+      </c>
+      <c r="C25" s="59" t="inlineStr">
+        <is>
+          <t>1 — Negligible</t>
+        </is>
+      </c>
+      <c r="D25" s="59" t="inlineStr">
+        <is>
+          <t>2 — Minor</t>
+        </is>
+      </c>
+      <c r="E25" s="59" t="inlineStr">
+        <is>
+          <t>3 — Moderate</t>
+        </is>
+      </c>
+      <c r="F25" s="59" t="inlineStr">
+        <is>
+          <t>4 — Significant</t>
+        </is>
+      </c>
+      <c r="G25" s="59" t="inlineStr">
+        <is>
+          <t>5 — Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1" s="27">
+      <c r="B26" s="60" t="inlineStr">
+        <is>
+          <t>5 — Almost Certain</t>
+        </is>
+      </c>
+      <c r="C26" s="61">
+        <f t="array" ref="C26">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=5)*('Risk Register'!$G$16:$G$31=1),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+      <c r="D26" s="62">
+        <f t="array" ref="D26">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=5)*('Risk Register'!$G$16:$G$31=2),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+      <c r="E26" s="63">
+        <f t="array" ref="E26">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=5)*('Risk Register'!$G$16:$G$31=3),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+      <c r="F26" s="63">
+        <f t="array" ref="F26">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=5)*('Risk Register'!$G$16:$G$31=4),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+      <c r="G26" s="63">
+        <f t="array" ref="G26">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=5)*('Risk Register'!$G$16:$G$31=5),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1" s="27">
+      <c r="B27" s="60" t="inlineStr">
+        <is>
+          <t>4 — Likely</t>
+        </is>
+      </c>
+      <c r="C27" s="61">
+        <f t="array" ref="C27">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=4)*('Risk Register'!$G$16:$G$31=1),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+      <c r="D27" s="62">
+        <f t="array" ref="D27">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=4)*('Risk Register'!$G$16:$G$31=2),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+      <c r="E27" s="62">
+        <f t="array" ref="E27">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=4)*('Risk Register'!$G$16:$G$31=3),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+      <c r="F27" s="63">
+        <f t="array" ref="F27">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=4)*('Risk Register'!$G$16:$G$31=4),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+      <c r="G27" s="63">
+        <f t="array" ref="G27">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=4)*('Risk Register'!$G$16:$G$31=5),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1" s="27">
+      <c r="B28" s="60" t="inlineStr">
+        <is>
+          <t>3 — Possible</t>
+        </is>
+      </c>
+      <c r="C28" s="61">
+        <f t="array" ref="C28">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=3)*('Risk Register'!$G$16:$G$31=1),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+      <c r="D28" s="61">
+        <f t="array" ref="D28">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=3)*('Risk Register'!$G$16:$G$31=2),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+      <c r="E28" s="62">
+        <f t="array" ref="E28">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=3)*('Risk Register'!$G$16:$G$31=3),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+      <c r="F28" s="62">
+        <f t="array" ref="F28">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=3)*('Risk Register'!$G$16:$G$31=4),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+      <c r="G28" s="63">
+        <f t="array" ref="G28">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=3)*('Risk Register'!$G$16:$G$31=5),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="34" customHeight="1" s="27">
+      <c r="B29" s="60" t="inlineStr">
+        <is>
+          <t>2 — Unlikely</t>
+        </is>
+      </c>
+      <c r="C29" s="61">
+        <f t="array" ref="C29">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=2)*('Risk Register'!$G$16:$G$31=1),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+      <c r="D29" s="61">
+        <f t="array" ref="D29">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=2)*('Risk Register'!$G$16:$G$31=2),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+      <c r="E29" s="61">
+        <f t="array" ref="E29">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=2)*('Risk Register'!$G$16:$G$31=3),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+      <c r="F29" s="62">
+        <f t="array" ref="F29">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=2)*('Risk Register'!$G$16:$G$31=4),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+      <c r="G29" s="62">
+        <f t="array" ref="G29">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=2)*('Risk Register'!$G$16:$G$31=5),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="34" customHeight="1" s="27">
+      <c r="B30" s="60" t="inlineStr">
+        <is>
+          <t>1 — Rare</t>
+        </is>
+      </c>
+      <c r="C30" s="61">
+        <f t="array" ref="C30">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=1)*('Risk Register'!$G$16:$G$31=1),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+      <c r="D30" s="61">
+        <f t="array" ref="D30">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=1)*('Risk Register'!$G$16:$G$31=2),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+      <c r="E30" s="61">
+        <f t="array" ref="E30">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=1)*('Risk Register'!$G$16:$G$31=3),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+      <c r="F30" s="61">
+        <f t="array" ref="F30">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=1)*('Risk Register'!$G$16:$G$31=4),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+      <c r="G30" s="61">
+        <f t="array" ref="G30">_xlfn.TEXTJOIN(", ",TRUE,IF(('Risk Register'!$F$16:$F$31=1)*('Risk Register'!$G$16:$G$31=5),'Risk Register'!$B$16:$B$31,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="64" t="inlineStr">
+        <is>
+          <t>Blank cell = no risk currently scored at that Probability × Impact combination.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="65" t="inlineStr">
+        <is>
+          <t>License &amp; Use</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="57" t="inlineStr">
+        <is>
+          <t>This template is licensed for use on one program, by one organization, under your Acqlerate purchase. Customize the text, branding, and layout freely for your own program. Deploying it company-wide, sharing it outside your organization, or reselling it requires an Acqlerate Team License (acqlerate.com/team).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="6">
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B2:G2"/>
@@ -2236,6 +2589,6 @@
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>